--- a/astro-site/public/dl/restaurant-business-plan/restaurant-financial-projections.xlsx
+++ b/astro-site/public/dl/restaurant-business-plan/restaurant-financial-projections.xlsx
@@ -1130,7 +1130,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Monthly rent for a space of about 2,800 sq ft in an urban area (NNN rent plus CAM charges, if your lease has them), kept under the 10% of sales ceiling that this workbook flags. Replace it with the rent in your lease or your broker's quote</t>
+          <t>Total monthly occupancy cost for a space of about 2,800 sq ft in an urban area: base rent plus estimated NNN / CAM charges (property tax, building insurance and common-area maintenance), kept under the 10% of sales ceiling that this workbook flags. Replace it with your lease: if it quotes base rent only, add those charges here</t>
         </is>
       </c>
     </row>
@@ -7299,10 +7299,10 @@
       <c r="D6" s="44" t="n"/>
       <c r="E6" s="44" t="n"/>
     </row>
-    <row r="7" ht="75" customHeight="1">
+    <row r="7" ht="89.75" customHeight="1">
       <c r="A7" s="63" t="inlineStr">
         <is>
-          <t>3. On "3. Break-Even" you only type the seat-turn ceiling your space allows; everything else derives from the rest. The other tabs also have green cells you can change: the pessimistic and optimistic scenarios on "4. Scenarios", the seasonality and the launch ramp-up on "6. 12-Month Cash Flow", and the four alternative financing sources on "7. Financing". Everything else is calculated.</t>
+          <t>3. On "3. Break-Even" you only type the seat-turn ceiling your space allows; everything else derives from the rest. The other tabs also have green cells you can change: the pessimistic and optimistic scenarios on "4. Scenarios", the seasonality and the launch ramp-up on "6. 12-Month Cash Flow", and the other funding sources on "7. Financing" (rows 8-11 count as sources but are not amortized: your bank or SBA 7(a) loan goes in "Loan requested" on "0. Assumptions"). Everything else is calculated.</t>
         </is>
       </c>
       <c r="B7" s="44" t="n"/>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C51" s="44" t="inlineStr">
         <is>
-          <t>Papaya (papaya.co.th)</t>
+          <t>Kit estimate</t>
         </is>
       </c>
       <c r="D51" s="63" t="n"/>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="C52" s="44" t="inlineStr">
         <is>
-          <t>Papaya (papaya.co.th)</t>
+          <t>Kit estimate</t>
         </is>
       </c>
       <c r="D52" s="63" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="C9" s="44" t="inlineStr">
         <is>
-          <t>SBA Microloans go up to $50,000 through nonprofit intermediaries. Like row 8, a source of funds only: not in the schedule or the DSCR. If it is your only loan, enter it in row 7 instead</t>
+          <t>SBA Microloans go up to 50,000 through nonprofit intermediaries. Like row 8, a source of funds only: not in the schedule or the DSCR. If it is your only loan, enter it in row 7 instead</t>
         </is>
       </c>
       <c r="D9" s="44" t="n"/>

--- a/astro-site/public/dl/restaurant-business-plan/restaurant-financial-projections.xlsx
+++ b/astro-site/public/dl/restaurant-business-plan/restaurant-financial-projections.xlsx
@@ -2900,7 +2900,7 @@
       </c>
       <c r="C55" s="44" t="n"/>
       <c r="D55" s="41" t="str">
-        <f>IFERROR("Not depreciated, because they are not fixed assets: broker and lease review fees, security deposit, pre-opening rent, brand design, website and Google Business Profile, grand opening campaign, entity formation and legal, liquor license and permits, opening food and bar inventory and the working capital reserve. They add up to "&amp;TEXT(B48-B53-B54,"#,##0")&amp;" of the "&amp;TEXT(B48,"#,##0")&amp;" total investment.","")</f>
+        <f>IFERROR("Not depreciated, because they are not fixed assets: broker and lease review fees, security deposit, pre-opening rent, brand design, website and Google Business Profile, grand opening campaign, entity formation and legal, liquor license and "&amp;"permits, opening food and bar inventory and the working capital reserve. They add up to "&amp;TEXT(B48-B53-B54,"#,##0")&amp;" of the "&amp;TEXT(B48,"#,##0")&amp;" total investment.","")</f>
         <v>Not depreciated, because they are not fixed assets: broker and lease review fees, security deposit, pre-opening rent, brand design, website and Google Business Profile, grand opening campaign, entity formation and legal, liquor license and permits, opening food and bar inventory and the working capital reserve. They add up to 215496 of the 528696 total investment.</v>
       </c>
       <c r="E55" s="44" t="n"/>
@@ -9259,7 +9259,7 @@
       </c>
       <c r="O20" s="44" t="inlineStr">
         <is>
-          <t>Cash only leaves when the quarter's result is positive. Months without a settlement are left blank, not zero. The cell turns RED when the payment takes more cash than is left that month. The model settles quarterly (April, July, October, January): if your state requires monthly filing, expect smaller payments every month instead</t>
+          <t>Cash only leaves when the quarter's result is positive. Months without a settlement are left blank, not zero. The cell turns RED when the payment takes more cash than is left that month. The model settles quarterly, in the month after each plan quarter (Months 4, 7 and 10, and the fourth quarter in Month 13: April, July, October and January when Month 1 is January): if your state requires monthly filing, expect smaller payments every month instead</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/restaurant-business-plan/restaurant-financial-projections.xlsx
+++ b/astro-site/public/dl/restaurant-business-plan/restaurant-financial-projections.xlsx
@@ -1689,7 +1689,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>How far you can fall below plan before you start losing money</t>
+          <t>How far planned sales must sit above cash break-even (fixed costs and the loan payment). The drop you can absorb is somewhat smaller: with a 15% cushion, about 13% of plan</t>
         </is>
       </c>
     </row>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="E25" s="44" t="inlineStr">
         <is>
-          <t>How far you can fall before you cannot pay the fixed costs and the loan payment. The required minimum is set in the "0. Assumptions" tab</t>
+          <t>How far planned sales sit above cash break-even. The drop you can absorb before you cannot pay the fixed costs and the loan payment is somewhat smaller: with a 25% cushion, 20%. The required minimum is set in the "0. Assumptions" tab</t>
         </is>
       </c>
       <c r="F25" s="44" t="n"/>
@@ -9673,7 +9673,7 @@
     <row r="34" ht="134.75" customHeight="1">
       <c r="A34" s="63" t="inlineStr">
         <is>
-          <t>Fourth-quarter sales tax is settled in January of the following year, so it does not appear in this table. The model pays year-1 income tax in July of year 2 (a simplification: estimated tax payments are usually quarterly). The loan payment is spread in twelve equal parts following the ANNUAL schedule in the Financing tab, and payroll in twelve monthly installments (plus extra pay periods in their month, only if pay periods &gt; 12).</t>
+          <t>Fourth-quarter sales tax is settled in Month 13 (January of the following year when Month 1 is January), so it does not appear in this table. The model pays year-1 income tax in July of year 2 (a simplification: estimated tax payments are usually quarterly). The loan payment is spread in twelve equal parts following the ANNUAL schedule in the Financing tab, and payroll in twelve monthly installments (plus extra pay periods in their month, only if pay periods &gt; 12).</t>
         </is>
       </c>
       <c r="B34" s="44" t="n"/>

--- a/astro-site/public/dl/restaurant-business-plan/restaurant-financial-projections.xlsx
+++ b/astro-site/public/dl/restaurant-business-plan/restaurant-financial-projections.xlsx
@@ -1689,7 +1689,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>How far you can fall below plan before you start losing money</t>
+          <t>How far planned sales must sit above cash break-even (fixed costs and the loan payment). The drop you can absorb is somewhat smaller: with a 15% cushion, about 13% of plan</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="C55" s="44" t="n"/>
       <c r="D55" s="41" t="str">
-        <f>IFERROR("Not depreciated, because they are not fixed assets: broker and lease review fees, security deposit, pre-opening rent, brand design, website and Google Business Profile, grand opening campaign, entity formation and legal, liquor license and permits, opening food and bar inventory and the working capital reserve. They add up to "&amp;TEXT(B48-B53-B54,"#,##0")&amp;" of the "&amp;TEXT(B48,"#,##0")&amp;" total investment.","")</f>
+        <f>IFERROR("Not depreciated, because they are not fixed assets: broker and lease review fees, security deposit, pre-opening rent, brand design, website and Google Business Profile, grand opening campaign, entity formation and legal, liquor license and "&amp;"permits, opening food and bar inventory and the working capital reserve. They add up to "&amp;TEXT(B48-B53-B54,"#,##0")&amp;" of the "&amp;TEXT(B48,"#,##0")&amp;" total investment.","")</f>
         <v>Not depreciated, because they are not fixed assets: broker and lease review fees, security deposit, pre-opening rent, brand design, website and Google Business Profile, grand opening campaign, entity formation and legal, liquor license and permits, opening food and bar inventory and the working capital reserve. They add up to 215496 of the 528696 total investment.</v>
       </c>
       <c r="E55" s="44" t="n"/>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="E25" s="44" t="inlineStr">
         <is>
-          <t>How far you can fall before you cannot pay the fixed costs and the loan payment. The required minimum is set in the "0. Assumptions" tab</t>
+          <t>How far planned sales sit above cash break-even. The drop you can absorb before you cannot pay the fixed costs and the loan payment is somewhat smaller: with a 25% cushion, 20%. The required minimum is set in the "0. Assumptions" tab</t>
         </is>
       </c>
       <c r="F25" s="44" t="n"/>
@@ -9259,7 +9259,7 @@
       </c>
       <c r="O20" s="44" t="inlineStr">
         <is>
-          <t>Cash only leaves when the quarter's result is positive. Months without a settlement are left blank, not zero. The cell turns RED when the payment takes more cash than is left that month. The model settles quarterly (April, July, October, January): if your state requires monthly filing, expect smaller payments every month instead</t>
+          <t>Cash only leaves when the quarter's result is positive. Months without a settlement are left blank, not zero. The cell turns RED when the payment takes more cash than is left that month. The model settles quarterly, in the month after each plan quarter (Months 4, 7 and 10, and the fourth quarter in Month 13: April, July, October and January when Month 1 is January): if your state requires monthly filing, expect smaller payments every month instead</t>
         </is>
       </c>
     </row>
@@ -9673,7 +9673,7 @@
     <row r="34" ht="134.75" customHeight="1">
       <c r="A34" s="63" t="inlineStr">
         <is>
-          <t>Fourth-quarter sales tax is settled in January of the following year, so it does not appear in this table. The model pays year-1 income tax in July of year 2 (a simplification: estimated tax payments are usually quarterly). The loan payment is spread in twelve equal parts following the ANNUAL schedule in the Financing tab, and payroll in twelve monthly installments (plus extra pay periods in their month, only if pay periods &gt; 12).</t>
+          <t>Fourth-quarter sales tax is settled in Month 13 (January of the following year when Month 1 is January), so it does not appear in this table. The model pays year-1 income tax in July of year 2 (a simplification: estimated tax payments are usually quarterly). The loan payment is spread in twelve equal parts following the ANNUAL schedule in the Financing tab, and payroll in twelve monthly installments (plus extra pay periods in their month, only if pay periods &gt; 12).</t>
         </is>
       </c>
       <c r="B34" s="44" t="n"/>

--- a/astro-site/public/dl/restaurant-business-plan/restaurant-financial-projections.xlsx
+++ b/astro-site/public/dl/restaurant-business-plan/restaurant-financial-projections.xlsx
@@ -9670,7 +9670,7 @@
       <c r="N33" s="44" t="n"/>
       <c r="O33" s="44" t="n"/>
     </row>
-    <row r="34" ht="134.75" customHeight="1">
+    <row r="34" ht="149.5" customHeight="1">
       <c r="A34" s="63" t="inlineStr">
         <is>
           <t>Fourth-quarter sales tax is settled in Month 13 (January of the following year when Month 1 is January), so it does not appear in this table. The model pays year-1 income tax in July of year 2 (a simplification: estimated tax payments are usually quarterly). The loan payment is spread in twelve equal parts following the ANNUAL schedule in the Financing tab, and payroll in twelve monthly installments (plus extra pay periods in their month, only if pay periods &gt; 12).</t>
